--- a/mapping/Bacteria.xlsx
+++ b/mapping/Bacteria.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2770"/>
+  <dimension ref="A1:B2909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>异腔菌属</t>
+          <t>异鞘菌属</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>鞘氨醇盒菌属</t>
+          <t>鞘脂杆菌属</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>红长命菌属</t>
+          <t>红活菌属</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>淡水土杆菌属</t>
+          <t>甜水杆菌属</t>
         </is>
       </c>
     </row>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>海洋杆状微菌属</t>
+          <t>海杆微菌属</t>
         </is>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>囊杆菌属</t>
+          <t>囊菌属</t>
         </is>
       </c>
     </row>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>未知菌属</t>
+          <t>未知属</t>
         </is>
       </c>
     </row>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>纡曲螺菌属</t>
+          <t>新螺菌属</t>
         </is>
       </c>
     </row>
@@ -15856,7 +15856,7 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>贪食杆菌属</t>
+          <t>伪足菌属</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>内孢囊菌属</t>
+          <t>孢内菌属</t>
         </is>
       </c>
     </row>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>松土杆菌属</t>
+          <t>松栖菌属</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>褐指藻杆菌属</t>
+          <t>褐指杆菌属</t>
         </is>
       </c>
     </row>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>速生杆菌属</t>
+          <t>速杆菌属</t>
         </is>
       </c>
     </row>
@@ -17596,7 +17596,7 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>海洋热丝菌属</t>
+          <t>海热丝菌属</t>
         </is>
       </c>
     </row>
@@ -17872,7 +17872,7 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>莫拉球菌属</t>
+          <t>桑球菌属</t>
         </is>
       </c>
     </row>
@@ -21472,7 +21472,7 @@
       </c>
       <c r="B1755" t="inlineStr">
         <is>
-          <t>玛拉密截菌属</t>
+          <t>消瘦菌属</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21508,7 @@
       </c>
       <c r="B1758" t="inlineStr">
         <is>
-          <t>玫瑰环状球菌</t>
+          <t>玫红环菌属</t>
         </is>
       </c>
     </row>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="B1785" t="inlineStr">
         <is>
-          <t>鞘丝蓝细菌属</t>
+          <t>束丝藻属</t>
         </is>
       </c>
     </row>
@@ -22012,7 +22012,7 @@
       </c>
       <c r="B1800" t="inlineStr">
         <is>
-          <t>闪光杆菌属</t>
+          <t>薄层菌属</t>
         </is>
       </c>
     </row>
@@ -22612,7 +22612,7 @@
       </c>
       <c r="B1850" t="inlineStr">
         <is>
-          <t>喜盐刺丝菌属</t>
+          <t>盐棘毛菌属</t>
         </is>
       </c>
     </row>
@@ -23212,7 +23212,7 @@
       </c>
       <c r="B1900" t="inlineStr">
         <is>
-          <t>棕色小壶菌属</t>
+          <t>褐色菌属</t>
         </is>
       </c>
     </row>
@@ -23548,7 +23548,7 @@
       </c>
       <c r="B1928" t="inlineStr">
         <is>
-          <t>需氧菌属</t>
+          <t>气菌属</t>
         </is>
       </c>
     </row>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="B1954" t="inlineStr">
         <is>
-          <t>深渊栖菌属</t>
+          <t>深渊菌属</t>
         </is>
       </c>
     </row>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="B2051" t="inlineStr">
         <is>
-          <t>考沙克氏菌属</t>
+          <t>科扎克菌属</t>
         </is>
       </c>
     </row>
@@ -25168,7 +25168,7 @@
       </c>
       <c r="B2063" t="inlineStr">
         <is>
-          <t>远洋杆菌属</t>
+          <t>海杆菌属</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25456,7 @@
       </c>
       <c r="B2087" t="inlineStr">
         <is>
-          <t>阿托波菌属</t>
+          <t>奇异菌属</t>
         </is>
       </c>
     </row>
@@ -27232,7 +27232,7 @@
       </c>
       <c r="B2235" t="inlineStr">
         <is>
-          <t>根杆状菌属</t>
+          <t>根棍菌属</t>
         </is>
       </c>
     </row>
@@ -27256,7 +27256,7 @@
       </c>
       <c r="B2237" t="inlineStr">
         <is>
-          <t>碱性脱硫弧菌属</t>
+          <t>碱脱硫弧菌属</t>
         </is>
       </c>
     </row>
@@ -27964,7 +27964,7 @@
       </c>
       <c r="B2296" t="inlineStr">
         <is>
-          <t>暂定名纳米共生菌属</t>
+          <t>暂定纳米共生菌属</t>
         </is>
       </c>
     </row>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="B2309" t="inlineStr">
         <is>
-          <t>石生乳杆菌属</t>
+          <t>石乳杆菌属</t>
         </is>
       </c>
     </row>
@@ -28156,7 +28156,7 @@
       </c>
       <c r="B2312" t="inlineStr">
         <is>
-          <t>滑粘球菌属</t>
+          <t>湿粘菌属</t>
         </is>
       </c>
     </row>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="B2313" t="inlineStr">
         <is>
-          <t>鞘氨醇盒菌属</t>
+          <t>鞘脂小菌属</t>
         </is>
       </c>
     </row>
@@ -28684,7 +28684,7 @@
       </c>
       <c r="B2356" t="inlineStr">
         <is>
-          <t>中栖热菌属</t>
+          <t>稍热菌属</t>
         </is>
       </c>
     </row>
@@ -29608,7 +29608,7 @@
       </c>
       <c r="B2433" t="inlineStr">
         <is>
-          <t>海洋杆菌属</t>
+          <t>海杆菌属</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="B2516" t="inlineStr">
         <is>
-          <t>泡菜杆菌属</t>
+          <t>酱香菌属</t>
         </is>
       </c>
     </row>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="B2518" t="inlineStr">
         <is>
-          <t>土壤湖杆菌属</t>
+          <t>溶土杆菌属</t>
         </is>
       </c>
     </row>
@@ -31216,7 +31216,7 @@
       </c>
       <c r="B2567" t="inlineStr">
         <is>
-          <t>塞德塞亚菌属</t>
+          <t>西地西菌属</t>
         </is>
       </c>
     </row>
@@ -31252,7 +31252,7 @@
       </c>
       <c r="B2570" t="inlineStr">
         <is>
-          <t>烷降解菌属</t>
+          <t>嗜烷菌属</t>
         </is>
       </c>
     </row>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="B2573" t="inlineStr">
         <is>
-          <t>埃内氏菌属</t>
+          <t>敌害菌属</t>
         </is>
       </c>
     </row>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="B2583" t="inlineStr">
         <is>
-          <t>立克次氏体属</t>
+          <t>立克次体属</t>
         </is>
       </c>
     </row>
@@ -31456,7 +31456,7 @@
       </c>
       <c r="B2587" t="inlineStr">
         <is>
-          <t>海洋杆菌属</t>
+          <t>海杆菌属</t>
         </is>
       </c>
     </row>
@@ -31624,7 +31624,7 @@
       </c>
       <c r="B2601" t="inlineStr">
         <is>
-          <t>植物栖菌属</t>
+          <t>植栖菌属</t>
         </is>
       </c>
     </row>
@@ -32704,7 +32704,7 @@
       </c>
       <c r="B2691" t="inlineStr">
         <is>
-          <t>平面细菌属</t>
+          <t>平丝菌属</t>
         </is>
       </c>
     </row>
@@ -32812,7 +32812,7 @@
       </c>
       <c r="B2700" t="inlineStr">
         <is>
-          <t>甜美绳蓝细菌属</t>
+          <t>甜钙丝菌属</t>
         </is>
       </c>
     </row>
@@ -32980,7 +32980,7 @@
       </c>
       <c r="B2714" t="inlineStr">
         <is>
-          <t>红色微杆菌属</t>
+          <t>微红菌属</t>
         </is>
       </c>
     </row>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="B2718" t="inlineStr">
         <is>
-          <t>新鞘氨醇盒菌属</t>
+          <t>新鞘脂杆菌属</t>
         </is>
       </c>
     </row>
@@ -33436,7 +33436,7 @@
       </c>
       <c r="B2752" t="inlineStr">
         <is>
-          <t>异鞘氨醇小菌属</t>
+          <t>异鞘脂小菌属</t>
         </is>
       </c>
     </row>
@@ -33479,180 +33479,1848 @@
     <row r="2756">
       <c r="A2756" t="inlineStr">
         <is>
-          <t>Kyrpidia</t>
+          <t>Maliponia</t>
         </is>
       </c>
       <c r="B2756" t="inlineStr">
         <is>
-          <t>克尔氏菌属</t>
+          <t>马里波尼亚菌属</t>
         </is>
       </c>
     </row>
     <row r="2757">
       <c r="A2757" t="inlineStr">
         <is>
-          <t>Pelagivirga</t>
+          <t>Kytococcus</t>
         </is>
       </c>
       <c r="B2757" t="inlineStr">
         <is>
-          <t>海洋杆状菌属</t>
+          <t>皮球菌属</t>
         </is>
       </c>
     </row>
     <row r="2758">
       <c r="A2758" t="inlineStr">
         <is>
-          <t>Holospora</t>
+          <t>Peptoanaerobacter</t>
         </is>
       </c>
       <c r="B2758" t="inlineStr">
         <is>
-          <t>全孢菌属</t>
+          <t>消化厌氧杆菌属</t>
         </is>
       </c>
     </row>
     <row r="2759">
       <c r="A2759" t="inlineStr">
         <is>
-          <t>Thermobispora</t>
+          <t>Barrientosiimonas</t>
         </is>
       </c>
       <c r="B2759" t="inlineStr">
         <is>
-          <t>热双孢菌属</t>
+          <t>巴里恩托斯氏单胞菌属</t>
         </is>
       </c>
     </row>
     <row r="2760">
       <c r="A2760" t="inlineStr">
         <is>
-          <t>Pajaroellobacter</t>
+          <t>Paucidesulfovibrio</t>
         </is>
       </c>
       <c r="B2760" t="inlineStr">
         <is>
-          <t>帕哈罗杆菌属</t>
+          <t>贫脱硫弧菌属</t>
         </is>
       </c>
     </row>
     <row r="2761">
       <c r="A2761" t="inlineStr">
         <is>
-          <t>Siculibacillus</t>
+          <t>Flaviflexus</t>
         </is>
       </c>
       <c r="B2761" t="inlineStr">
         <is>
-          <t>镰刀形芽孢杆菌属</t>
+          <t>黄弯曲菌属</t>
         </is>
       </c>
     </row>
     <row r="2762">
       <c r="A2762" t="inlineStr">
         <is>
-          <t>Metamycoplasma</t>
+          <t>Hydrocarboniclastica</t>
         </is>
       </c>
       <c r="B2762" t="inlineStr">
         <is>
-          <t>代谢支原体属</t>
+          <t>解烃菌属</t>
         </is>
       </c>
     </row>
     <row r="2763">
       <c r="A2763" t="inlineStr">
         <is>
-          <t>Imhoffiella</t>
+          <t>Histidinibacterium</t>
         </is>
       </c>
       <c r="B2763" t="inlineStr">
         <is>
-          <t>英霍夫氏菌属</t>
+          <t>组氨酸杆菌属</t>
         </is>
       </c>
     </row>
     <row r="2764">
       <c r="A2764" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Scardovia</t>
         </is>
       </c>
       <c r="B2764" t="inlineStr">
         <is>
-          <t>新兴菌属</t>
+          <t>斯卡多维亚菌属</t>
         </is>
       </c>
     </row>
     <row r="2765">
       <c r="A2765" t="inlineStr">
         <is>
-          <t>Hominifimenecus</t>
+          <t>Mycetocola</t>
         </is>
       </c>
       <c r="B2765" t="inlineStr">
         <is>
-          <t>人栖小杆菌属</t>
+          <t>栖真菌菌属</t>
         </is>
       </c>
     </row>
     <row r="2766">
       <c r="A2766" t="inlineStr">
         <is>
-          <t>Anaplasma</t>
+          <t>Neogemmobacter</t>
         </is>
       </c>
       <c r="B2766" t="inlineStr">
         <is>
-          <t>无形体属</t>
+          <t>新芽殖杆菌属</t>
         </is>
       </c>
     </row>
     <row r="2767">
       <c r="A2767" t="inlineStr">
         <is>
-          <t>Streptobacillus</t>
+          <t>Fenollaria</t>
         </is>
       </c>
       <c r="B2767" t="inlineStr">
         <is>
-          <t>链杆菌属</t>
+          <t>费诺拉菌属</t>
         </is>
       </c>
     </row>
     <row r="2768">
       <c r="A2768" t="inlineStr">
         <is>
-          <t>Merdimmobilis</t>
+          <t>Pseudaeromonas</t>
         </is>
       </c>
       <c r="B2768" t="inlineStr">
         <is>
-          <t>粪固着菌属</t>
+          <t>假气单胞菌属</t>
         </is>
       </c>
     </row>
     <row r="2769">
       <c r="A2769" t="inlineStr">
         <is>
-          <t>Candidatus Neoarthromitus</t>
+          <t>Luteipulveratus</t>
         </is>
       </c>
       <c r="B2769" t="inlineStr">
         <is>
-          <t>候选新节膜菌属</t>
+          <t>黄粉菌属</t>
         </is>
       </c>
     </row>
     <row r="2770">
       <c r="A2770" t="inlineStr">
         <is>
+          <t>Facklamia</t>
+        </is>
+      </c>
+      <c r="B2770" t="inlineStr">
+        <is>
+          <t>法克兰氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="A2771" t="inlineStr">
+        <is>
+          <t>Alloyangia</t>
+        </is>
+      </c>
+      <c r="B2771" t="inlineStr">
+        <is>
+          <t>异杨氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="A2772" t="inlineStr">
+        <is>
+          <t>Methylobrevis</t>
+        </is>
+      </c>
+      <c r="B2772" t="inlineStr">
+        <is>
+          <t>短甲基菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="A2773" t="inlineStr">
+        <is>
+          <t>Aliterella</t>
+        </is>
+      </c>
+      <c r="B2773" t="inlineStr">
+        <is>
+          <t>异样菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" t="inlineStr">
+        <is>
+          <t>Chroococcus</t>
+        </is>
+      </c>
+      <c r="B2774" t="inlineStr">
+        <is>
+          <t>色球藻属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" t="inlineStr">
+        <is>
+          <t>Gardnerella</t>
+        </is>
+      </c>
+      <c r="B2775" t="inlineStr">
+        <is>
+          <t>加德纳氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" t="inlineStr">
+        <is>
+          <t>Acaricomes</t>
+        </is>
+      </c>
+      <c r="B2776" t="inlineStr">
+        <is>
+          <t>螨栖菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="A2777" t="inlineStr">
+        <is>
+          <t>Tuberibacillus</t>
+        </is>
+      </c>
+      <c r="B2777" t="inlineStr">
+        <is>
+          <t>块茎芽孢杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="A2778" t="inlineStr">
+        <is>
+          <t>Prevotellamassilia</t>
+        </is>
+      </c>
+      <c r="B2778" t="inlineStr">
+        <is>
+          <t>普雷沃氏马赛菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="A2779" t="inlineStr">
+        <is>
+          <t>Pikeienuella</t>
+        </is>
+      </c>
+      <c r="B2779" t="inlineStr">
+        <is>
+          <t>皮凯耶努菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="A2780" t="inlineStr">
+        <is>
+          <t>Terricaulis</t>
+        </is>
+      </c>
+      <c r="B2780" t="inlineStr">
+        <is>
+          <t>土竿菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="A2781" t="inlineStr">
+        <is>
+          <t>Candidatus Minimicrobia</t>
+        </is>
+      </c>
+      <c r="B2781" t="inlineStr">
+        <is>
+          <t>暂定微小菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2782">
+      <c r="A2782" t="inlineStr">
+        <is>
+          <t>Merdimmobilis</t>
+        </is>
+      </c>
+      <c r="B2782" t="inlineStr">
+        <is>
+          <t>固粪菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" t="inlineStr">
+        <is>
+          <t>Faecalitalea</t>
+        </is>
+      </c>
+      <c r="B2783" t="inlineStr">
+        <is>
+          <t>粪泰勒菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="A2784" t="inlineStr">
+        <is>
+          <t>Stakelama</t>
+        </is>
+      </c>
+      <c r="B2784" t="inlineStr">
+        <is>
+          <t>斯塔克拉马菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="A2785" t="inlineStr">
+        <is>
+          <t>Aliidiomarina</t>
+        </is>
+      </c>
+      <c r="B2785" t="inlineStr">
+        <is>
+          <t>异伊迪奥马菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2786">
+      <c r="A2786" t="inlineStr">
+        <is>
+          <t>Litorisediminicola</t>
+        </is>
+      </c>
+      <c r="B2786" t="inlineStr">
+        <is>
+          <t>海岸沉积物栖菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="A2787" t="inlineStr">
+        <is>
+          <t>Neoaquamicrobium</t>
+        </is>
+      </c>
+      <c r="B2787" t="inlineStr">
+        <is>
+          <t>新水微菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="A2788" t="inlineStr">
+        <is>
+          <t>Acidimangrovimonas</t>
+        </is>
+      </c>
+      <c r="B2788" t="inlineStr">
+        <is>
+          <t>嗜酸红树林单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="A2789" t="inlineStr">
+        <is>
+          <t>Oceaniradius</t>
+        </is>
+      </c>
+      <c r="B2789" t="inlineStr">
+        <is>
+          <t>海半径菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2790">
+      <c r="A2790" t="inlineStr">
+        <is>
+          <t>Breoghania</t>
+        </is>
+      </c>
+      <c r="B2790" t="inlineStr">
+        <is>
+          <t>布雷奥加尼亚菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="A2791" t="inlineStr">
+        <is>
+          <t>Pontivivens</t>
+        </is>
+      </c>
+      <c r="B2791" t="inlineStr">
+        <is>
+          <t>桥活菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" t="inlineStr">
+        <is>
+          <t>Cryocola</t>
+        </is>
+      </c>
+      <c r="B2792" t="inlineStr">
+        <is>
+          <t>冷居菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="A2793" t="inlineStr">
+        <is>
+          <t>Rhodothalassium</t>
+        </is>
+      </c>
+      <c r="B2793" t="inlineStr">
+        <is>
+          <t>红海藻菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="A2794" t="inlineStr">
+        <is>
+          <t>Denitratimonas</t>
+        </is>
+      </c>
+      <c r="B2794" t="inlineStr">
+        <is>
+          <t>脱硝单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" t="inlineStr">
+        <is>
+          <t>Halodurantibacterium</t>
+        </is>
+      </c>
+      <c r="B2795" t="inlineStr">
+        <is>
+          <t>耐盐杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="A2796" t="inlineStr">
+        <is>
+          <t>Acidaminobacter</t>
+        </is>
+      </c>
+      <c r="B2796" t="inlineStr">
+        <is>
+          <t>嗜氨基酸杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="A2797" t="inlineStr">
+        <is>
+          <t>Metamycoplasma</t>
+        </is>
+      </c>
+      <c r="B2797" t="inlineStr">
+        <is>
+          <t>后支原体属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" t="inlineStr">
+        <is>
+          <t>Citreimonas</t>
+        </is>
+      </c>
+      <c r="B2798" t="inlineStr">
+        <is>
+          <t>柠檬单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" t="inlineStr">
+        <is>
+          <t>Brevirhabdus</t>
+        </is>
+      </c>
+      <c r="B2799" t="inlineStr">
+        <is>
+          <t>短棍菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="A2800" t="inlineStr">
+        <is>
+          <t>Ursidibacter</t>
+        </is>
+      </c>
+      <c r="B2800" t="inlineStr">
+        <is>
+          <t>熊杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" t="inlineStr">
+        <is>
+          <t>Aliiroseovarius</t>
+        </is>
+      </c>
+      <c r="B2801" t="inlineStr">
+        <is>
+          <t>异玫瑰弧菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="A2802" t="inlineStr">
+        <is>
+          <t>Gudongella</t>
+        </is>
+      </c>
+      <c r="B2802" t="inlineStr">
+        <is>
+          <t>古东菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="A2803" t="inlineStr">
+        <is>
+          <t>Stomatobaculum</t>
+        </is>
+      </c>
+      <c r="B2803" t="inlineStr">
+        <is>
+          <t>口小杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="A2804" t="inlineStr">
+        <is>
+          <t>Propionimicrobium</t>
+        </is>
+      </c>
+      <c r="B2804" t="inlineStr">
+        <is>
+          <t>丙酸微菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="A2805" t="inlineStr">
+        <is>
+          <t>Streptobacillus</t>
+        </is>
+      </c>
+      <c r="B2805" t="inlineStr">
+        <is>
+          <t>链杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" t="inlineStr">
+        <is>
+          <t>Soonwooa</t>
+        </is>
+      </c>
+      <c r="B2806" t="inlineStr">
+        <is>
+          <t>顺宇氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="A2807" t="inlineStr">
+        <is>
+          <t>Kordiimonas</t>
+        </is>
+      </c>
+      <c r="B2807" t="inlineStr">
+        <is>
+          <t>科迪单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="A2808" t="inlineStr">
+        <is>
+          <t>Urinicoccus</t>
+        </is>
+      </c>
+      <c r="B2808" t="inlineStr">
+        <is>
+          <t>尿球菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2809">
+      <c r="A2809" t="inlineStr">
+        <is>
+          <t>Laedolimicola</t>
+        </is>
+      </c>
+      <c r="B2809" t="inlineStr">
+        <is>
+          <t>莱多利米菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2810">
+      <c r="A2810" t="inlineStr">
+        <is>
+          <t>Oleidesulfovibrio</t>
+        </is>
+      </c>
+      <c r="B2810" t="inlineStr">
+        <is>
+          <t>油脱硫弧菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2811">
+      <c r="A2811" t="inlineStr">
+        <is>
+          <t>Metallococcus</t>
+        </is>
+      </c>
+      <c r="B2811" t="inlineStr">
+        <is>
+          <t>金属球菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2812">
+      <c r="A2812" t="inlineStr">
+        <is>
+          <t>Marimonas</t>
+        </is>
+      </c>
+      <c r="B2812" t="inlineStr">
+        <is>
+          <t>海单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2813">
+      <c r="A2813" t="inlineStr">
+        <is>
+          <t>Lwoffella</t>
+        </is>
+      </c>
+      <c r="B2813" t="inlineStr">
+        <is>
+          <t>卢夫氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2814">
+      <c r="A2814" t="inlineStr">
+        <is>
+          <t>Tropicimonas</t>
+        </is>
+      </c>
+      <c r="B2814" t="inlineStr">
+        <is>
+          <t>热带单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2815">
+      <c r="A2815" t="inlineStr">
+        <is>
+          <t>Pseudorhodobacter</t>
+        </is>
+      </c>
+      <c r="B2815" t="inlineStr">
+        <is>
+          <t>假红杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2816">
+      <c r="A2816" t="inlineStr">
+        <is>
+          <t>Pseudogemmobacter</t>
+        </is>
+      </c>
+      <c r="B2816" t="inlineStr">
+        <is>
+          <t>假芽殖杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2817">
+      <c r="A2817" t="inlineStr">
+        <is>
+          <t>Pauljensenia</t>
+        </is>
+      </c>
+      <c r="B2817" t="inlineStr">
+        <is>
+          <t>保罗-延森菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2818">
+      <c r="A2818" t="inlineStr">
+        <is>
+          <t>Micavibrio</t>
+        </is>
+      </c>
+      <c r="B2818" t="inlineStr">
+        <is>
+          <t>微弧菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2819">
+      <c r="A2819" t="inlineStr">
+        <is>
+          <t>Mesoflavibacter</t>
+        </is>
+      </c>
+      <c r="B2819" t="inlineStr">
+        <is>
+          <t>中黄杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2820">
+      <c r="A2820" t="inlineStr">
+        <is>
+          <t>Cognatishimia</t>
+        </is>
+      </c>
+      <c r="B2820" t="inlineStr">
+        <is>
+          <t>亲属志贺氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2821">
+      <c r="A2821" t="inlineStr">
+        <is>
+          <t>Macrococcoides</t>
+        </is>
+      </c>
+      <c r="B2821" t="inlineStr">
+        <is>
+          <t>大球菌样菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2822">
+      <c r="A2822" t="inlineStr">
+        <is>
+          <t>Aedoeadaptatus</t>
+        </is>
+      </c>
+      <c r="B2822" t="inlineStr">
+        <is>
+          <t>适应伊多菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2823">
+      <c r="A2823" t="inlineStr">
+        <is>
+          <t>Pseudoruegeria</t>
+        </is>
+      </c>
+      <c r="B2823" t="inlineStr">
+        <is>
+          <t>假鲁杰氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2824">
+      <c r="A2824" t="inlineStr">
+        <is>
+          <t>Pseudoprevotella</t>
+        </is>
+      </c>
+      <c r="B2824" t="inlineStr">
+        <is>
+          <t>假普雷沃氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2825">
+      <c r="A2825" t="inlineStr">
+        <is>
+          <t>Tropicibacter</t>
+        </is>
+      </c>
+      <c r="B2825" t="inlineStr">
+        <is>
+          <t>热带杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2826">
+      <c r="A2826" t="inlineStr">
+        <is>
+          <t>Alterirhizorhabdus</t>
+        </is>
+      </c>
+      <c r="B2826" t="inlineStr">
+        <is>
+          <t>交替根棍菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2827">
+      <c r="A2827" t="inlineStr">
+        <is>
+          <t>Mesobacterium</t>
+        </is>
+      </c>
+      <c r="B2827" t="inlineStr">
+        <is>
+          <t>中杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2828">
+      <c r="A2828" t="inlineStr">
+        <is>
+          <t>Simonsiella</t>
+        </is>
+      </c>
+      <c r="B2828" t="inlineStr">
+        <is>
+          <t>西蒙斯氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2829">
+      <c r="A2829" t="inlineStr">
+        <is>
+          <t>Profundibacterium</t>
+        </is>
+      </c>
+      <c r="B2829" t="inlineStr">
+        <is>
+          <t>深海杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2830">
+      <c r="A2830" t="inlineStr">
+        <is>
+          <t>Eisenbergiella</t>
+        </is>
+      </c>
+      <c r="B2830" t="inlineStr">
+        <is>
+          <t>艾森伯格氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2831">
+      <c r="A2831" t="inlineStr">
+        <is>
+          <t>Sodaliphilus</t>
+        </is>
+      </c>
+      <c r="B2831" t="inlineStr">
+        <is>
+          <t>钠嗜菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2832">
+      <c r="A2832" t="inlineStr">
+        <is>
+          <t>Ostreiculturibacter</t>
+        </is>
+      </c>
+      <c r="B2832" t="inlineStr">
+        <is>
+          <t>牡蛎养殖杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2833">
+      <c r="A2833" t="inlineStr">
+        <is>
+          <t>Weeksella</t>
+        </is>
+      </c>
+      <c r="B2833" t="inlineStr">
+        <is>
+          <t>威克斯氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2834">
+      <c r="A2834" t="inlineStr">
+        <is>
+          <t>Acidipropionibacterium</t>
+        </is>
+      </c>
+      <c r="B2834" t="inlineStr">
+        <is>
+          <t>酸丙酸杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2835">
+      <c r="A2835" t="inlineStr">
+        <is>
+          <t>Aquicoccus</t>
+        </is>
+      </c>
+      <c r="B2835" t="inlineStr">
+        <is>
+          <t>水球菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2836">
+      <c r="A2836" t="inlineStr">
+        <is>
+          <t>Amniculibacterium</t>
+        </is>
+      </c>
+      <c r="B2836" t="inlineStr">
+        <is>
+          <t>小河杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2837">
+      <c r="A2837" t="inlineStr">
+        <is>
+          <t>Olleya</t>
+        </is>
+      </c>
+      <c r="B2837" t="inlineStr">
+        <is>
+          <t>奥利氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2838">
+      <c r="A2838" t="inlineStr">
+        <is>
+          <t>Miniimonas</t>
+        </is>
+      </c>
+      <c r="B2838" t="inlineStr">
+        <is>
+          <t>微小单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2839">
+      <c r="A2839" t="inlineStr">
+        <is>
+          <t>Neptunicoccus</t>
+        </is>
+      </c>
+      <c r="B2839" t="inlineStr">
+        <is>
+          <t>海神球菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2840">
+      <c r="A2840" t="inlineStr">
+        <is>
+          <t>Chlorogloea</t>
+        </is>
+      </c>
+      <c r="B2840" t="inlineStr">
+        <is>
+          <t>绿胶藻属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2841">
+      <c r="A2841" t="inlineStr">
+        <is>
+          <t>Thermaurantiacus</t>
+        </is>
+      </c>
+      <c r="B2841" t="inlineStr">
+        <is>
+          <t>热金黄菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2842">
+      <c r="A2842" t="inlineStr">
+        <is>
+          <t>Ponticaulis</t>
+        </is>
+      </c>
+      <c r="B2842" t="inlineStr">
+        <is>
+          <t>桥竿菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2843">
+      <c r="A2843" t="inlineStr">
+        <is>
+          <t>Oceaniglobus</t>
+        </is>
+      </c>
+      <c r="B2843" t="inlineStr">
+        <is>
+          <t>海洋球状菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2844">
+      <c r="A2844" t="inlineStr">
+        <is>
+          <t>Oenococcus</t>
+        </is>
+      </c>
+      <c r="B2844" t="inlineStr">
+        <is>
+          <t>酒球菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2845">
+      <c r="A2845" t="inlineStr">
+        <is>
+          <t>Bombella</t>
+        </is>
+      </c>
+      <c r="B2845" t="inlineStr">
+        <is>
+          <t>炸弹菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2846">
+      <c r="A2846" t="inlineStr">
+        <is>
+          <t>Parasphingopyxis</t>
+        </is>
+      </c>
+      <c r="B2846" t="inlineStr">
+        <is>
+          <t>副鞘脂杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2847">
+      <c r="A2847" t="inlineStr">
+        <is>
+          <t>Vaginella</t>
+        </is>
+      </c>
+      <c r="B2847" t="inlineStr">
+        <is>
+          <t>阴道菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2848">
+      <c r="A2848" t="inlineStr">
+        <is>
+          <t>Marivirga</t>
+        </is>
+      </c>
+      <c r="B2848" t="inlineStr">
+        <is>
+          <t>海活力菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2849">
+      <c r="A2849" t="inlineStr">
+        <is>
+          <t>Pseudoponticoccus</t>
+        </is>
+      </c>
+      <c r="B2849" t="inlineStr">
+        <is>
+          <t>假海桥球菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2850">
+      <c r="A2850" t="inlineStr">
+        <is>
+          <t>Cribrihabitans</t>
+        </is>
+      </c>
+      <c r="B2850" t="inlineStr">
+        <is>
+          <t>筛栖菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2851">
+      <c r="A2851" t="inlineStr">
+        <is>
+          <t>Pseudoroseicyclus</t>
+        </is>
+      </c>
+      <c r="B2851" t="inlineStr">
+        <is>
+          <t>假玫红环菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2852">
+      <c r="A2852" t="inlineStr">
+        <is>
+          <t>Criibacterium</t>
+        </is>
+      </c>
+      <c r="B2852" t="inlineStr">
+        <is>
+          <t>克里菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2853">
+      <c r="A2853" t="inlineStr">
+        <is>
+          <t>Epidermidibacterium</t>
+        </is>
+      </c>
+      <c r="B2853" t="inlineStr">
+        <is>
+          <t>表皮杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2854">
+      <c r="A2854" t="inlineStr">
+        <is>
+          <t>Phytobacter</t>
+        </is>
+      </c>
+      <c r="B2854" t="inlineStr">
+        <is>
+          <t>植杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2855">
+      <c r="A2855" t="inlineStr">
+        <is>
+          <t>Seramator</t>
+        </is>
+      </c>
+      <c r="B2855" t="inlineStr">
+        <is>
+          <t>塞拉马托菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2856">
+      <c r="A2856" t="inlineStr">
+        <is>
+          <t>Meridianimarinicoccus</t>
+        </is>
+      </c>
+      <c r="B2856" t="inlineStr">
+        <is>
+          <t>子午线海球菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2857">
+      <c r="A2857" t="inlineStr">
+        <is>
+          <t>Hominiventricola</t>
+        </is>
+      </c>
+      <c r="B2857" t="inlineStr">
+        <is>
+          <t>人胃栖菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2858">
+      <c r="A2858" t="inlineStr">
+        <is>
+          <t>Periweissella</t>
+        </is>
+      </c>
+      <c r="B2858" t="inlineStr">
+        <is>
+          <t>周魏斯氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2859">
+      <c r="A2859" t="inlineStr">
+        <is>
+          <t>Oceaniovalibus</t>
+        </is>
+      </c>
+      <c r="B2859" t="inlineStr">
+        <is>
+          <t>海洋卵形菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2860">
+      <c r="A2860" t="inlineStr">
+        <is>
+          <t>Oceanibium</t>
+        </is>
+      </c>
+      <c r="B2860" t="inlineStr">
+        <is>
+          <t>海洋菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2861">
+      <c r="A2861" t="inlineStr">
+        <is>
+          <t>Altericroceibacterium</t>
+        </is>
+      </c>
+      <c r="B2861" t="inlineStr">
+        <is>
+          <t>交替黄杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2862">
+      <c r="A2862" t="inlineStr">
+        <is>
+          <t>Ferruginivarius</t>
+        </is>
+      </c>
+      <c r="B2862" t="inlineStr">
+        <is>
+          <t>铁锈菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2863">
+      <c r="A2863" t="inlineStr">
+        <is>
+          <t>Nioella</t>
+        </is>
+      </c>
+      <c r="B2863" t="inlineStr">
+        <is>
+          <t>尼奥氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2864">
+      <c r="A2864" t="inlineStr">
+        <is>
+          <t>Marvinbryantia</t>
+        </is>
+      </c>
+      <c r="B2864" t="inlineStr">
+        <is>
+          <t>马文-布赖恩蒂亚菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2865">
+      <c r="A2865" t="inlineStr">
+        <is>
+          <t>Scrofimicrobium</t>
+        </is>
+      </c>
+      <c r="B2865" t="inlineStr">
+        <is>
+          <t>癣微菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2866">
+      <c r="A2866" t="inlineStr">
+        <is>
+          <t>Tianweitania</t>
+        </is>
+      </c>
+      <c r="B2866" t="inlineStr">
+        <is>
+          <t>天威坦菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" t="inlineStr">
+        <is>
+          <t>Epibacterium</t>
+        </is>
+      </c>
+      <c r="B2867" t="inlineStr">
+        <is>
+          <t>表皮杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="A2868" t="inlineStr">
+        <is>
+          <t>Roseinatronobacter</t>
+        </is>
+      </c>
+      <c r="B2868" t="inlineStr">
+        <is>
+          <t>玫瑰碱杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="A2869" t="inlineStr">
+        <is>
+          <t>Mangrovibacter</t>
+        </is>
+      </c>
+      <c r="B2869" t="inlineStr">
+        <is>
+          <t>红树林杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="A2870" t="inlineStr">
+        <is>
+          <t>Stagnihabitans</t>
+        </is>
+      </c>
+      <c r="B2870" t="inlineStr">
+        <is>
+          <t>静水栖菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="A2871" t="inlineStr">
+        <is>
+          <t>Alterinioella</t>
+        </is>
+      </c>
+      <c r="B2871" t="inlineStr">
+        <is>
+          <t>交替伊尼奥菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="A2872" t="inlineStr">
+        <is>
+          <t>Arenibaculum</t>
+        </is>
+      </c>
+      <c r="B2872" t="inlineStr">
+        <is>
+          <t>沙小杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="A2873" t="inlineStr">
+        <is>
+          <t>Fibrivirga</t>
+        </is>
+      </c>
+      <c r="B2873" t="inlineStr">
+        <is>
+          <t>纤维活力菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="A2874" t="inlineStr">
+        <is>
+          <t>Actibacterium</t>
+        </is>
+      </c>
+      <c r="B2874" t="inlineStr">
+        <is>
+          <t>放线杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="A2875" t="inlineStr">
+        <is>
+          <t>Roseisalinus</t>
+        </is>
+      </c>
+      <c r="B2875" t="inlineStr">
+        <is>
+          <t>玫红海盐菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="A2876" t="inlineStr">
+        <is>
+          <t>Pelagerythrobacter</t>
+        </is>
+      </c>
+      <c r="B2876" t="inlineStr">
+        <is>
+          <t>海红杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="A2877" t="inlineStr">
+        <is>
+          <t>Amnimonas</t>
+        </is>
+      </c>
+      <c r="B2877" t="inlineStr">
+        <is>
+          <t>羊膜菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="A2878" t="inlineStr">
+        <is>
+          <t>Borrelia</t>
+        </is>
+      </c>
+      <c r="B2878" t="inlineStr">
+        <is>
+          <t>疏螺旋体属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="A2879" t="inlineStr">
+        <is>
+          <t>Segniliparus</t>
+        </is>
+      </c>
+      <c r="B2879" t="inlineStr">
+        <is>
+          <t>慢脂肪菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="A2880" t="inlineStr">
+        <is>
+          <t>Frigoriflavimonas</t>
+        </is>
+      </c>
+      <c r="B2880" t="inlineStr">
+        <is>
+          <t>冷黄单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2881">
+      <c r="A2881" t="inlineStr">
+        <is>
+          <t>Sagittula</t>
+        </is>
+      </c>
+      <c r="B2881" t="inlineStr">
+        <is>
+          <t>矢状菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2882">
+      <c r="A2882" t="inlineStr">
+        <is>
+          <t>Lysinimonas</t>
+        </is>
+      </c>
+      <c r="B2882" t="inlineStr">
+        <is>
+          <t>赖氨酸单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="A2883" t="inlineStr">
+        <is>
+          <t>Lacimonas</t>
+        </is>
+      </c>
+      <c r="B2883" t="inlineStr">
+        <is>
+          <t>乳单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2884">
+      <c r="A2884" t="inlineStr">
+        <is>
+          <t>Frondihabitans</t>
+        </is>
+      </c>
+      <c r="B2884" t="inlineStr">
+        <is>
+          <t>叶栖菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="A2885" t="inlineStr">
+        <is>
+          <t>Peptococcus</t>
+        </is>
+      </c>
+      <c r="B2885" t="inlineStr">
+        <is>
+          <t>消化球菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2886">
+      <c r="A2886" t="inlineStr">
+        <is>
+          <t>Szabonella</t>
+        </is>
+      </c>
+      <c r="B2886" t="inlineStr">
+        <is>
+          <t>萨博内拉菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="A2887" t="inlineStr">
+        <is>
+          <t>Pontitalea</t>
+        </is>
+      </c>
+      <c r="B2887" t="inlineStr">
+        <is>
+          <t>桥泰勒菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2888">
+      <c r="A2888" t="inlineStr">
+        <is>
+          <t>Endobacter</t>
+        </is>
+      </c>
+      <c r="B2888" t="inlineStr">
+        <is>
+          <t>内杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2889">
+      <c r="A2889" t="inlineStr">
+        <is>
+          <t>Alkalibacterium</t>
+        </is>
+      </c>
+      <c r="B2889" t="inlineStr">
+        <is>
+          <t>碱杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2890">
+      <c r="A2890" t="inlineStr">
+        <is>
+          <t>Antarctobacter</t>
+        </is>
+      </c>
+      <c r="B2890" t="inlineStr">
+        <is>
+          <t>南极杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2891">
+      <c r="A2891" t="inlineStr">
+        <is>
+          <t>Sciscionella</t>
+        </is>
+      </c>
+      <c r="B2891" t="inlineStr">
+        <is>
+          <t>西雄内拉菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2892">
+      <c r="A2892" t="inlineStr">
+        <is>
+          <t>Kribbibacterium</t>
+        </is>
+      </c>
+      <c r="B2892" t="inlineStr">
+        <is>
+          <t>克里比杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2893">
+      <c r="A2893" t="inlineStr">
+        <is>
+          <t>Sinomicrobium</t>
+        </is>
+      </c>
+      <c r="B2893" t="inlineStr">
+        <is>
+          <t>中华微菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2894">
+      <c r="A2894" t="inlineStr">
+        <is>
+          <t>Flavisphingomonas</t>
+        </is>
+      </c>
+      <c r="B2894" t="inlineStr">
+        <is>
+          <t>黄鞘氨醇单胞菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2895">
+      <c r="A2895" t="inlineStr">
+        <is>
+          <t>Velocimicrobium</t>
+        </is>
+      </c>
+      <c r="B2895" t="inlineStr">
+        <is>
+          <t>速微菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2896">
+      <c r="A2896" t="inlineStr">
+        <is>
+          <t>Marnyiella</t>
+        </is>
+      </c>
+      <c r="B2896" t="inlineStr">
+        <is>
+          <t>马尼拉菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2897">
+      <c r="A2897" t="inlineStr">
+        <is>
+          <t>Thiosulfatihalobacter</t>
+        </is>
+      </c>
+      <c r="B2897" t="inlineStr">
+        <is>
+          <t>硫代硫酸盐盐杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2898">
+      <c r="A2898" t="inlineStr">
+        <is>
           <t>Sinobaca</t>
         </is>
       </c>
-      <c r="B2770" t="inlineStr">
-        <is>
-          <t>中华芽孢杆菌属</t>
+      <c r="B2898" t="inlineStr">
+        <is>
+          <t>中华杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2899">
+      <c r="A2899" t="inlineStr">
+        <is>
+          <t>Kyrpidia</t>
+        </is>
+      </c>
+      <c r="B2899" t="inlineStr">
+        <is>
+          <t>克尔氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2900">
+      <c r="A2900" t="inlineStr">
+        <is>
+          <t>Pelagivirga</t>
+        </is>
+      </c>
+      <c r="B2900" t="inlineStr">
+        <is>
+          <t>海洋杆状菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2901">
+      <c r="A2901" t="inlineStr">
+        <is>
+          <t>Holospora</t>
+        </is>
+      </c>
+      <c r="B2901" t="inlineStr">
+        <is>
+          <t>全孢菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2902">
+      <c r="A2902" t="inlineStr">
+        <is>
+          <t>Thermobispora</t>
+        </is>
+      </c>
+      <c r="B2902" t="inlineStr">
+        <is>
+          <t>热双孢菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2903">
+      <c r="A2903" t="inlineStr">
+        <is>
+          <t>Pajaroellobacter</t>
+        </is>
+      </c>
+      <c r="B2903" t="inlineStr">
+        <is>
+          <t>帕哈罗杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2904">
+      <c r="A2904" t="inlineStr">
+        <is>
+          <t>Siculibacillus</t>
+        </is>
+      </c>
+      <c r="B2904" t="inlineStr">
+        <is>
+          <t>镰刀形芽孢杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2905">
+      <c r="A2905" t="inlineStr">
+        <is>
+          <t>Imhoffiella</t>
+        </is>
+      </c>
+      <c r="B2905" t="inlineStr">
+        <is>
+          <t>英霍夫氏菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2906">
+      <c r="A2906" t="inlineStr">
+        <is>
+          <t>Emergencia</t>
+        </is>
+      </c>
+      <c r="B2906" t="inlineStr">
+        <is>
+          <t>新兴菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2907">
+      <c r="A2907" t="inlineStr">
+        <is>
+          <t>Hominifimenecus</t>
+        </is>
+      </c>
+      <c r="B2907" t="inlineStr">
+        <is>
+          <t>人栖小杆菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2908">
+      <c r="A2908" t="inlineStr">
+        <is>
+          <t>Anaplasma</t>
+        </is>
+      </c>
+      <c r="B2908" t="inlineStr">
+        <is>
+          <t>无形体属</t>
+        </is>
+      </c>
+    </row>
+    <row r="2909">
+      <c r="A2909" t="inlineStr">
+        <is>
+          <t>Candidatus Neoarthromitus</t>
+        </is>
+      </c>
+      <c r="B2909" t="inlineStr">
+        <is>
+          <t>候选新节膜菌属</t>
         </is>
       </c>
     </row>
